--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.83026246290044</v>
+        <v>7.122417650221321</v>
       </c>
       <c r="D2" t="n">
-        <v>44.31263590875859</v>
+        <v>7.200803335173272</v>
       </c>
       <c r="E2" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F2" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.65812224166775</v>
+        <v>7.581944864271009</v>
       </c>
       <c r="D3" t="n">
-        <v>46.77587028069888</v>
+        <v>7.601078920613568</v>
       </c>
       <c r="E3" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F3" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.89772348481177</v>
+        <v>5.995880066281913</v>
       </c>
       <c r="D4" t="n">
-        <v>37.51341167664785</v>
+        <v>6.095929397455276</v>
       </c>
       <c r="E4" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F4" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.93303807305281</v>
+        <v>5.839118686871083</v>
       </c>
       <c r="D5" t="n">
-        <v>36.22369826956881</v>
+        <v>5.886350968804932</v>
       </c>
       <c r="E5" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F5" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.43841498015807</v>
+        <v>3.808742434275687</v>
       </c>
       <c r="D6" t="n">
-        <v>24.08135130341902</v>
+        <v>3.913219586805591</v>
       </c>
       <c r="E6" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F6" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.2881752719211</v>
+        <v>3.621828481687179</v>
       </c>
       <c r="D7" t="n">
-        <v>22.68088308471908</v>
+        <v>3.68564350126685</v>
       </c>
       <c r="E7" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F7" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.16175753046321</v>
+        <v>6.363785598700272</v>
       </c>
       <c r="D8" t="n">
-        <v>38.99913641642707</v>
+        <v>6.337359667669399</v>
       </c>
       <c r="E8" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F8" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.1563651464129</v>
+        <v>6.362909336292096</v>
       </c>
       <c r="D9" t="n">
-        <v>39.6799686007609</v>
+        <v>6.447994897623647</v>
       </c>
       <c r="E9" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F9" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.769962393360438</v>
+        <v>1.262618888921071</v>
       </c>
       <c r="D10" t="n">
-        <v>8.371912243048605</v>
+        <v>1.360435739495398</v>
       </c>
       <c r="E10" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F10" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.583197714151484</v>
+        <v>1.232269628549616</v>
       </c>
       <c r="D11" t="n">
-        <v>7.451246123017153</v>
+        <v>1.210827494990288</v>
       </c>
       <c r="E11" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F11" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.10910034265829</v>
+        <v>3.755228805681972</v>
       </c>
       <c r="D12" t="n">
-        <v>23.54994792119061</v>
+        <v>3.826866537193475</v>
       </c>
       <c r="E12" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F12" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.48438487273923</v>
+        <v>7.878712541820126</v>
       </c>
       <c r="D13" t="n">
-        <v>32.06936925548185</v>
+        <v>5.211272504015802</v>
       </c>
       <c r="E13" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F13" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.6569291291596</v>
+        <v>5.631750983488435</v>
       </c>
       <c r="D14" t="n">
-        <v>34.94659368176876</v>
+        <v>5.678821473287424</v>
       </c>
       <c r="E14" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F14" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.15788387586774</v>
+        <v>7.175656129828508</v>
       </c>
       <c r="D15" t="n">
-        <v>26.50366850917896</v>
+        <v>4.306846132741581</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F15" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.03373250140567</v>
+        <v>5.042981531478421</v>
       </c>
       <c r="D16" t="n">
-        <v>12.64079381938487</v>
+        <v>2.054128995650041</v>
       </c>
       <c r="E16" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F16" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>36.99687869121966</v>
+        <v>6.011992787323195</v>
       </c>
       <c r="D17" t="n">
-        <v>37.01242718778872</v>
+        <v>6.014519418015668</v>
       </c>
       <c r="E17" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F17" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>40.6709985516168</v>
+        <v>6.609037264637731</v>
       </c>
       <c r="D18" t="n">
-        <v>20.19969746748148</v>
+        <v>3.282450838465741</v>
       </c>
       <c r="E18" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F18" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>23.33652342053272</v>
+        <v>3.792185055836567</v>
       </c>
       <c r="D19" t="n">
-        <v>23.26818418222437</v>
+        <v>3.78107992961146</v>
       </c>
       <c r="E19" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F19" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>17.03300487097144</v>
+        <v>2.767863291532859</v>
       </c>
       <c r="D20" t="n">
-        <v>16.99484974750852</v>
+        <v>2.761663083970135</v>
       </c>
       <c r="E20" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F20" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>14.85671048663979</v>
+        <v>2.414215454078965</v>
       </c>
       <c r="D21" t="n">
-        <v>14.87811703022521</v>
+        <v>2.417694017411597</v>
       </c>
       <c r="E21" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F21" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>27.30806930745442</v>
+        <v>4.437561262461343</v>
       </c>
       <c r="D22" t="n">
-        <v>27.35953061013603</v>
+        <v>4.445923724147105</v>
       </c>
       <c r="E22" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F22" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>22.75437780112692</v>
+        <v>3.697586392683124</v>
       </c>
       <c r="D23" t="n">
-        <v>22.72700662446853</v>
+        <v>3.693138576476136</v>
       </c>
       <c r="E23" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F23" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>13.56907269520568</v>
+        <v>2.204974312970923</v>
       </c>
       <c r="D24" t="n">
-        <v>13.56043291717177</v>
+        <v>2.203570349040413</v>
       </c>
       <c r="E24" t="n">
-        <v>12.08940738559432</v>
+        <v>1.964528700159078</v>
       </c>
       <c r="F24" t="n">
-        <v>11.14624116868552</v>
+        <v>1.811264189911398</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
